--- a/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 13,22</t>
+          <t>1,48; 12,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 31,61</t>
+          <t>5,61; 29,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 26,54</t>
+          <t>7,84; 25,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 9,57</t>
+          <t>1,07; 10,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,73</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,98; 25,03</t>
+          <t>6,54; 26,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 31,53</t>
+          <t>11,34; 29,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 15,02</t>
+          <t>3,06; 15,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,91</t>
+          <t>1,12; 6,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 23,09</t>
+          <t>7,79; 22,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 24,65</t>
+          <t>11,59; 24,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,74; 10,0</t>
+          <t>2,69; 9,91</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 13,44</t>
+          <t>3,67; 13,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 13,63</t>
+          <t>2,39; 13,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,65; 22,85</t>
+          <t>9,01; 22,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,31</t>
+          <t>1,23; 8,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,83; 18,46</t>
+          <t>5,94; 18,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 18,16</t>
+          <t>4,66; 17,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 14,56</t>
+          <t>4,12; 14,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 18,44</t>
+          <t>6,56; 17,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 13,41</t>
+          <t>5,82; 14,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,84</t>
+          <t>4,73; 13,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 16,4</t>
+          <t>7,65; 16,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 11,57</t>
+          <t>4,58; 11,61</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 13,58</t>
+          <t>2,3; 13,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,35</t>
+          <t>1,7; 14,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,07</t>
+          <t>1,23; 10,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,98; 26,47</t>
+          <t>10,62; 26,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 16,43</t>
+          <t>5,44; 15,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 12,25</t>
+          <t>1,21; 11,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,22</t>
+          <t>1,1; 10,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 17,58</t>
+          <t>4,55; 16,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 12,91</t>
+          <t>4,86; 12,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,42; 9,66</t>
+          <t>2,52; 9,98</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,29</t>
+          <t>1,69; 8,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 17,9</t>
+          <t>7,73; 17,46</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 13,85</t>
+          <t>3,1; 13,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 13,68</t>
+          <t>1,7; 13,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,31; 28,26</t>
+          <t>9,31; 27,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 11,76</t>
+          <t>0,71; 11,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 13,87</t>
+          <t>2,29; 13,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 18,94</t>
+          <t>4,39; 20,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 23,07</t>
+          <t>6,07; 23,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 14,48</t>
+          <t>1,25; 13,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 11,59</t>
+          <t>3,5; 11,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 14,22</t>
+          <t>3,86; 13,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 21,1</t>
+          <t>9,03; 21,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 9,7</t>
+          <t>1,76; 9,89</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,6</t>
+          <t>0,0; 43,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 31,13</t>
+          <t>3,64; 31,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 20,47</t>
+          <t>2,3; 20,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,63</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,37</t>
+          <t>0,0; 30,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,31; 33,2</t>
+          <t>6,41; 31,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 14,8</t>
+          <t>0,0; 14,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,05</t>
+          <t>0,0; 18,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 23,93</t>
+          <t>3,33; 26,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 28,86</t>
+          <t>6,98; 25,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,08; 13,87</t>
+          <t>3,33; 14,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,43</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,32 +1417,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,96</t>
+          <t>1,49; 13,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,4</t>
+          <t>0,0; 11,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,78</t>
+          <t>0,0; 14,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 10,01</t>
+          <t>0,84; 9,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,32</t>
+          <t>0,0; 7,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,27</t>
+          <t>1,47; 12,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,34 +1452,34 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,65; 26,38</t>
+          <t>7,43; 26,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,05</t>
+          <t>1,39; 7,64</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,66</t>
+          <t>1,52; 8,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 6,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,07; 16,27</t>
+          <t>5,33; 16,69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 12,58</t>
+          <t>4,42; 12,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,96; 22,03</t>
+          <t>10,91; 21,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,34</t>
+          <t>1,13; 7,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 16,75</t>
+          <t>7,26; 17,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,98</t>
+          <t>5,38; 13,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,53; 17,93</t>
+          <t>7,11; 17,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,28</t>
+          <t>2,26; 9,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,84; 18,91</t>
+          <t>8,23; 18,6</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,68; 11,98</t>
+          <t>5,94; 11,87</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,12; 17,59</t>
+          <t>10,29; 18,23</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,72</t>
+          <t>2,23; 6,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,01; 16,22</t>
+          <t>9,14; 15,82</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,09</t>
+          <t>1,56; 8,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,83; 17,53</t>
+          <t>7,46; 16,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,81; 12,9</t>
+          <t>4,93; 12,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,85</t>
+          <t>0,73; 5,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,32; 17,62</t>
+          <t>7,42; 17,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,19</t>
+          <t>4,05; 11,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,65</t>
+          <t>0,98; 5,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,05</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,75; 12,09</t>
+          <t>5,94; 12,35</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,57; 12,42</t>
+          <t>6,58; 12,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,82</t>
+          <t>3,55; 7,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,21</t>
+          <t>0,74; 3,23</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,53</t>
+          <t>5,06; 8,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,53</t>
+          <t>8,05; 12,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,48</t>
+          <t>6,66; 10,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,65</t>
+          <t>4,54; 7,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,3; 9,94</t>
+          <t>6,36; 10,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,56</t>
+          <t>7,33; 11,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,45</t>
+          <t>5,07; 8,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,31</t>
+          <t>6,52; 10,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,62</t>
+          <t>6,0; 8,64</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,28; 11,27</t>
+          <t>8,21; 11,23</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,9</t>
+          <t>6,39; 9,04</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,98; 8,59</t>
+          <t>6,02; 8,46</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,79%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3864</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6804</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2754</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5100</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10172</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>5875</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8964</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>16976</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8630</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>707; 5844</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1421; 7455</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3560; 11755</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>785; 7629</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3888</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2491; 9972</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5896; 15452</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2430; 12206</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1106; 6642</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4939; 14045</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>11283; 24189</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4113; 15129</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>5113</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3475</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10574</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4879</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>5921</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6817</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>14472</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12351</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>9396</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>17391</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>19351</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2490; 9473</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1302; 7596</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>6373; 16149</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1570; 10785</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3855; 12289</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2743; 10552</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3296; 11521</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>8369; 22583</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>7729; 18703</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>5359; 15033</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>11523; 24619</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>11679; 29628</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>4387</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2177</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9770</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>6228</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>3089</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6014</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>10614</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6028</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5171</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>15784</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1487; 8811</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>895; 7846</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>715; 5927</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6137; 15541</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3697; 10553</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>722; 7133</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>726; 6995</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3041; 11245</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6440; 16222</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>2843; 11239</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2096; 10331</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9636; 21755</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4516</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2580</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7420</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2794</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4771</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5514</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3830</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>9287</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>8094</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13443</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>6625</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2045; 9017</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>843; 6646</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4201; 12580</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>492; 7798</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1687; 9655</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2438; 11155</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2895; 11260</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>979; 10526</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4892; 16495</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>4056; 14491</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>8381; 19755</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2591; 14571</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2121</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6198</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2070</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4196</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>657; 5686</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744; 6665</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2392</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3522</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1580; 7840</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5056</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 7516</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>696; 5561</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2980; 10969</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2258; 9661</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 8122</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1450</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1542</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2273</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>7934</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3453</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>3723</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9475</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>698; 6307</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5055</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4002</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>381; 4390</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3691</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>728; 6141</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 0</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>4174; 14663</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1372; 7559</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1432; 8288</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3867</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>5412; 16957</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>8438</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>18578</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3815</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>14212</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>10167</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>14122</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>20637</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>18605</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>32700</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>9577</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>34849</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>4886; 14055</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>12732; 25485</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1317; 8200</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>9012; 21731</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5961; 15037</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>8660; 21486</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2679; 10829</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>12806; 28922</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>13155; 26276</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>24547; 43475</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5231; 15215</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>25564; 44225</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3949</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>13509</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>10387</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>11694</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3930</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>15643</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>22771</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>14317</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>4741</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1393; 7866</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>8617; 19578</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>6388; 16448</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>936; 6637</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>7165; 17356</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>5280; 14529</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>1364; 7886</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4701</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>11030; 22932</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>16196; 31163</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>9535; 21314</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>2098; 9177</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>32961</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>48489</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>44723</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>62086</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>75112</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>82468</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>101524</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>25409; 43683</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>38389; 61454</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>34963; 56558</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>29988; 51536</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>33619; 53681</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>39493; 62706</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>28904; 49272</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>49592; 77792</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>61797; 89101</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>83350; 114106</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>70008; 99045</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>85519; 120247</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 12,25</t>
+          <t>1,11; 10,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 29,4</t>
+          <t>4,84; 28,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,84; 25,9</t>
+          <t>7,46; 27,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,07; 10,41</t>
+          <t>1,01; 9,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 7,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,54; 26,19</t>
+          <t>6,32; 27,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,34; 29,72</t>
+          <t>11,79; 30,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,06; 15,38</t>
+          <t>3,11; 15,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,72</t>
+          <t>1,14; 7,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,79; 22,14</t>
+          <t>7,89; 23,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,59; 24,84</t>
+          <t>11,43; 25,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,91</t>
+          <t>2,63; 9,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 13,95</t>
+          <t>3,69; 13,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 13,97</t>
+          <t>2,33; 13,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,01; 22,84</t>
+          <t>9,25; 23,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 8,45</t>
+          <t>1,2; 7,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 18,92</t>
+          <t>6,16; 19,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,66; 17,92</t>
+          <t>5,31; 18,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 14,4</t>
+          <t>4,84; 15,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,56; 17,7</t>
+          <t>6,68; 17,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 14,08</t>
+          <t>5,71; 14,24</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 13,27</t>
+          <t>5,01; 14,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,65; 16,34</t>
+          <t>7,97; 16,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,58; 11,61</t>
+          <t>4,57; 11,65</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 13,62</t>
+          <t>3,13; 13,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 14,88</t>
+          <t>1,39; 12,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 10,2</t>
+          <t>1,23; 10,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,62; 26,89</t>
+          <t>9,7; 24,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 15,54</t>
+          <t>4,57; 16,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,9</t>
+          <t>1,22; 12,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,57</t>
+          <t>1,47; 11,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 16,84</t>
+          <t>4,19; 16,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 12,23</t>
+          <t>4,96; 12,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,98</t>
+          <t>2,13; 9,91</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,31</t>
+          <t>1,75; 8,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 17,46</t>
+          <t>8,3; 18,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 13,65</t>
+          <t>2,5; 13,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 13,38</t>
+          <t>0,0; 13,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 27,88</t>
+          <t>9,46; 28,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 11,28</t>
+          <t>0,91; 11,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 13,13</t>
+          <t>2,96; 12,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 20,11</t>
+          <t>4,15; 19,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,07; 23,63</t>
+          <t>6,25; 22,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 13,47</t>
+          <t>1,16; 12,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 11,82</t>
+          <t>3,86; 12,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 13,78</t>
+          <t>3,99; 13,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,03; 21,3</t>
+          <t>9,09; 21,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 9,89</t>
+          <t>1,48; 9,43</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,98</t>
+          <t>0,0; 43,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 31,51</t>
+          <t>3,65; 28,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 20,59</t>
+          <t>2,36; 21,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 7,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,9</t>
+          <t>0,0; 25,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,41; 31,83</t>
+          <t>5,87; 32,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,24</t>
+          <t>1,67; 15,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,46</t>
+          <t>0,0; 18,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 26,56</t>
+          <t>3,3; 24,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,98; 25,7</t>
+          <t>6,96; 25,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 14,23</t>
+          <t>3,16; 13,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 10,77</t>
         </is>
       </c>
     </row>
@@ -1417,32 +1417,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,52</t>
+          <t>1,5; 13,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,35</t>
+          <t>0,0; 11,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>0,0; 16,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,66</t>
+          <t>0,85; 10,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,06</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,4</t>
+          <t>1,44; 11,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,43; 26,1</t>
+          <t>7,29; 26,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 7,64</t>
+          <t>1,38; 7,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,81</t>
+          <t>1,49; 8,71</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,59</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 16,69</t>
+          <t>5,19; 17,02</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 12,7</t>
+          <t>4,35; 12,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,91; 21,84</t>
+          <t>10,69; 22,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,07</t>
+          <t>1,13; 6,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,26; 17,51</t>
+          <t>7,2; 16,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 13,57</t>
+          <t>5,44; 14,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,11; 17,64</t>
+          <t>7,1; 17,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,26; 9,14</t>
+          <t>2,19; 8,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 18,6</t>
+          <t>8,69; 19,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,94; 11,87</t>
+          <t>5,64; 11,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,29; 18,23</t>
+          <t>10,17; 18,13</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,49</t>
+          <t>2,28; 6,45</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,14; 15,82</t>
+          <t>9,34; 16,51</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,56; 8,83</t>
+          <t>1,44; 8,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 16,94</t>
+          <t>7,87; 17,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 12,69</t>
+          <t>4,93; 12,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,17</t>
+          <t>0,95; 6,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 17,97</t>
+          <t>7,3; 17,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,14</t>
+          <t>3,71; 11,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,66</t>
+          <t>0,99; 5,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,23; 3,36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,94; 12,35</t>
+          <t>5,66; 12,47</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,67</t>
+          <t>6,62; 12,52</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,93</t>
+          <t>3,66; 7,87</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,23</t>
+          <t>0,78; 3,24</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,7</t>
+          <t>4,96; 8,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,05; 12,88</t>
+          <t>8,18; 12,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,78</t>
+          <t>6,62; 10,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,81</t>
+          <t>4,47; 7,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,16</t>
+          <t>6,19; 10,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,33; 11,64</t>
+          <t>7,1; 11,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,07; 8,64</t>
+          <t>5,02; 8,55</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,52; 10,23</t>
+          <t>6,46; 10,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,64</t>
+          <t>5,97; 8,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,23</t>
+          <t>8,18; 11,2</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,04</t>
+          <t>6,2; 8,78</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,02; 8,46</t>
+          <t>6,09; 8,67</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>707; 5844</t>
+          <t>530; 5245</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1421; 7455</t>
+          <t>1228; 7150</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3560; 11755</t>
+          <t>3384; 12690</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>785; 7629</t>
+          <t>744; 7023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3888</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2491; 9972</t>
+          <t>2406; 10314</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5896; 15452</t>
+          <t>6129; 15893</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2430; 12206</t>
+          <t>2465; 12684</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1106; 6642</t>
+          <t>1127; 7034</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4939; 14045</t>
+          <t>5006; 14631</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11283; 24189</t>
+          <t>11133; 24669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4113; 15129</t>
+          <t>4018; 15058</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2490; 9473</t>
+          <t>2508; 9032</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1302; 7596</t>
+          <t>1266; 7442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6373; 16149</t>
+          <t>6537; 16700</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1570; 10785</t>
+          <t>1528; 10144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3855; 12289</t>
+          <t>4000; 12599</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2743; 10552</t>
+          <t>3125; 10964</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3296; 11521</t>
+          <t>3869; 12193</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8369; 22583</t>
+          <t>8530; 22667</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7729; 18703</t>
+          <t>7589; 18908</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5359; 15033</t>
+          <t>5672; 15854</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11523; 24619</t>
+          <t>12012; 24727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11679; 29628</t>
+          <t>11653; 29734</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1487; 8811</t>
+          <t>2023; 8993</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>895; 7846</t>
+          <t>731; 6355</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>715; 5927</t>
+          <t>715; 5852</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6137; 15541</t>
+          <t>5607; 14168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3697; 10553</t>
+          <t>3105; 11224</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>722; 7133</t>
+          <t>731; 7540</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>726; 6995</t>
+          <t>976; 7534</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3041; 11245</t>
+          <t>2800; 10720</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6440; 16222</t>
+          <t>6578; 16789</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2843; 11239</t>
+          <t>2397; 11161</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2096; 10331</t>
+          <t>2173; 10877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9636; 21755</t>
+          <t>10342; 22647</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2045; 9017</t>
+          <t>1651; 8705</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>843; 6646</t>
+          <t>0; 6712</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4201; 12580</t>
+          <t>4266; 12960</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>492; 7798</t>
+          <t>626; 7745</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1687; 9655</t>
+          <t>2179; 8963</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2438; 11155</t>
+          <t>2303; 10997</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2895; 11260</t>
+          <t>2980; 10723</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>979; 10526</t>
+          <t>908; 9686</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4892; 16495</t>
+          <t>5385; 17227</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4056; 14491</t>
+          <t>4191; 14257</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8381; 19755</t>
+          <t>8436; 19815</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2591; 14571</t>
+          <t>2176; 13885</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4196</t>
+          <t>0; 4140</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>657; 5686</t>
+          <t>659; 5063</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>744; 6665</t>
+          <t>765; 6966</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2392</t>
+          <t>0; 2753</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3522</t>
+          <t>0; 2879</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1580; 7840</t>
+          <t>1447; 7977</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5056</t>
+          <t>593; 5533</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 7516</t>
+          <t>0; 7336</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>696; 5561</t>
+          <t>690; 5037</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2980; 10969</t>
+          <t>2968; 10670</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2258; 9661</t>
+          <t>2148; 9242</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 8122</t>
+          <t>0; 8102</t>
         </is>
       </c>
     </row>
@@ -3249,32 +3249,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>698; 6307</t>
+          <t>698; 6370</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5055</t>
+          <t>0; 4907</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 4402</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>381; 4390</t>
+          <t>388; 4543</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3691</t>
+          <t>0; 3325</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>728; 6141</t>
+          <t>715; 5657</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4174; 14663</t>
+          <t>4098; 14665</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1372; 7559</t>
+          <t>1361; 7646</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1432; 8288</t>
+          <t>1406; 8195</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3867</t>
+          <t>0; 3664</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5412; 16957</t>
+          <t>5274; 17295</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4886; 14055</t>
+          <t>4809; 14006</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12732; 25485</t>
+          <t>12477; 26022</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1317; 8200</t>
+          <t>1312; 7805</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9012; 21731</t>
+          <t>8932; 21018</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5961; 15037</t>
+          <t>6025; 16133</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8660; 21486</t>
+          <t>8648; 21256</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2679; 10829</t>
+          <t>2598; 10465</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12806; 28922</t>
+          <t>13520; 29896</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13155; 26276</t>
+          <t>12478; 25787</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24547; 43475</t>
+          <t>24257; 43229</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5231; 15215</t>
+          <t>5357; 15121</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>25564; 44225</t>
+          <t>26128; 46161</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1393; 7866</t>
+          <t>1285; 7855</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>8617; 19578</t>
+          <t>9088; 19808</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6388; 16448</t>
+          <t>6395; 15904</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>936; 6637</t>
+          <t>1219; 7722</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7165; 17356</t>
+          <t>7050; 17123</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5280; 14529</t>
+          <t>4838; 14563</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1364; 7886</t>
+          <t>1377; 7981</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4701</t>
+          <t>359; 5242</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>11030; 22932</t>
+          <t>10510; 23153</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16196; 31163</t>
+          <t>16283; 30791</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9535; 21314</t>
+          <t>9850; 21153</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2098; 9177</t>
+          <t>2223; 9207</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>25409; 43683</t>
+          <t>24919; 42812</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>38389; 61454</t>
+          <t>39011; 60340</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34963; 56558</t>
+          <t>34721; 55716</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29988; 51536</t>
+          <t>29505; 50292</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>33619; 53681</t>
+          <t>32699; 53374</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>39493; 62706</t>
+          <t>38238; 61357</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28904; 49272</t>
+          <t>28628; 48785</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>49592; 77792</t>
+          <t>49117; 77960</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>61797; 89101</t>
+          <t>61541; 88920</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>83350; 114106</t>
+          <t>83051; 113810</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70008; 99045</t>
+          <t>67923; 96114</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>85519; 120247</t>
+          <t>86545; 123106</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,57%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4,93%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>15,24%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>14,99%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,56%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,99</t>
+          <t>0,0; 6,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 28,2</t>
+          <t>5,98; 25,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 27,96</t>
+          <t>11,56; 31,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,58</t>
+          <t>2,71; 12,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,19</t>
+          <t>1,48; 13,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 27,09</t>
+          <t>6,06; 31,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,79; 30,57</t>
+          <t>8,07; 26,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,11; 15,98</t>
+          <t>1,16; 10,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,11</t>
+          <t>1,1; 6,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,89; 23,06</t>
+          <t>8,01; 23,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,43; 25,33</t>
+          <t>11,56; 24,65</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,86</t>
+          <t>2,76; 9,35</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11,46%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>7,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>6,39%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>14,96%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,69; 13,3</t>
+          <t>5,83; 18,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 13,68</t>
+          <t>4,82; 18,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 23,62</t>
+          <t>4,4; 14,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,95</t>
+          <t>6,78; 18,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,16; 19,4</t>
+          <t>3,64; 13,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,31; 18,62</t>
+          <t>2,37; 13,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,84; 15,24</t>
+          <t>8,65; 22,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,68; 17,76</t>
+          <t>2,04; 10,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 14,24</t>
+          <t>5,26; 13,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 14,0</t>
+          <t>4,67; 12,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 16,41</t>
+          <t>8,07; 16,4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,65</t>
+          <t>5,51; 12,85</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,81%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,78%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,58%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>3,75%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,15%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 13,9</t>
+          <t>4,59; 16,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 12,06</t>
+          <t>1,64; 12,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>1,96; 11,22</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4,35; 17,39</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2,4; 13,58</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,31; 13,35</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>1,23; 10,07</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>9,7; 24,51</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,57; 16,53</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 12,58</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,47; 11,38</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 16,05</t>
+          <t>10,84; 25,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 12,66</t>
+          <t>4,91; 12,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,91</t>
+          <t>2,42; 9,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,75</t>
+          <t>1,75; 8,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 18,18</t>
+          <t>8,24; 17,62</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,19%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16,45%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 13,18</t>
+          <t>2,45; 13,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,51</t>
+          <t>4,03; 18,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 28,73</t>
+          <t>5,89; 23,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 11,2</t>
+          <t>0,93; 16,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 12,19</t>
+          <t>2,51; 13,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,15; 19,82</t>
+          <t>1,68; 13,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 22,5</t>
+          <t>8,31; 28,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 12,4</t>
+          <t>0,74; 9,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 12,34</t>
+          <t>3,62; 11,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,99; 13,56</t>
+          <t>3,82; 14,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,09; 21,36</t>
+          <t>8,89; 21,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 9,43</t>
+          <t>1,63; 9,35</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16,66%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>14,84%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>11,61%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,89%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,66%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,4</t>
+          <t>0,0; 25,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 28,06</t>
+          <t>6,31; 33,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 21,52</t>
+          <t>1,71; 14,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,98</t>
+          <t>0,0; 10,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,26</t>
+          <t>0,0; 44,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 32,39</t>
+          <t>3,67; 31,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 15,58</t>
+          <t>2,32; 20,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,02</t>
+          <t>0,0; 7,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 24,05</t>
+          <t>3,32; 23,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,96; 25,0</t>
+          <t>7,14; 28,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 13,61</t>
+          <t>3,08; 13,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,77</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,98%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3,25%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,44%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 13,65</t>
+          <t>0,0; 7,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,02</t>
+          <t>1,45; 12,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,13</t>
+          <t>0,0; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 10,0</t>
+          <t>7,82; 27,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>1,51; 14,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 11,42</t>
+          <t>0,0; 11,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,0</t>
+          <t>0,0; 13,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,29; 26,1</t>
+          <t>0,72; 9,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,73</t>
+          <t>1,36; 7,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,71</t>
+          <t>1,52; 8,66</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,19; 17,02</t>
+          <t>4,89; 15,58</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,18%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,6%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13,74%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7,63%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>15,92%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3,29%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11,45%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,18%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,66</t>
+          <t>5,43; 13,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 22,3</t>
+          <t>7,53; 17,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 6,72</t>
+          <t>2,18; 9,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 16,94</t>
+          <t>9,26; 19,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,44; 14,56</t>
+          <t>4,0; 12,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,1; 17,45</t>
+          <t>10,96; 22,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,83</t>
+          <t>1,12; 6,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,69; 19,22</t>
+          <t>7,41; 17,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,64; 11,65</t>
+          <t>5,68; 11,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,17; 18,13</t>
+          <t>10,12; 17,59</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,45</t>
+          <t>2,37; 6,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 16,51</t>
+          <t>9,27; 16,57</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7,1%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>4,43%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>8,01%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>7,1%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,82</t>
+          <t>7,32; 17,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7,87; 17,14</t>
+          <t>4,05; 11,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,93; 12,27</t>
+          <t>0,95; 5,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,01</t>
+          <t>0,19; 2,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,3; 17,73</t>
+          <t>2,06; 9,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 11,16</t>
+          <t>7,83; 17,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,73</t>
+          <t>4,81; 12,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,36</t>
+          <t>1,33; 6,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 12,47</t>
+          <t>5,75; 12,09</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,52</t>
+          <t>6,57; 12,42</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,87</t>
+          <t>3,47; 7,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,24</t>
+          <t>0,96; 3,86</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>8,52%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,97%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,52</t>
+          <t>6,3; 9,94</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,65</t>
+          <t>7,17; 11,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,62</t>
+          <t>5,07; 8,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,62</t>
+          <t>6,14; 9,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,1</t>
+          <t>4,96; 8,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,1; 11,39</t>
+          <t>7,93; 12,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,55</t>
+          <t>6,55; 10,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,25</t>
+          <t>4,92; 8,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,63</t>
+          <t>5,97; 8,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8,18; 11,2</t>
+          <t>8,28; 11,27</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,78</t>
+          <t>6,37; 8,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,09; 8,67</t>
+          <t>6,02; 8,56</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5100</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10172</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4214</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2354</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3864</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>6804</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2754</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5100</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10172</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5875</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>6568</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>530; 5245</t>
+          <t>0; 3446</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1228; 7150</t>
+          <t>2279; 9532</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3384; 12690</t>
+          <t>6010; 16395</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>744; 7023</t>
+          <t>1740; 8327</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3681</t>
+          <t>706; 6305</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2406; 10314</t>
+          <t>1536; 8014</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6129; 15893</t>
+          <t>3661; 12044</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2465; 12684</t>
+          <t>657; 5800</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1127; 7034</t>
+          <t>1086; 6833</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5006; 14631</t>
+          <t>5082; 14645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11133; 24669</t>
+          <t>11255; 24001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4018; 15058</t>
+          <t>3328; 11274</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>7238</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5921</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6817</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13276</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5113</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3475</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>10574</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7238</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5921</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>6817</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>18393</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2508; 9032</t>
+          <t>3787; 11985</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1266; 7442</t>
+          <t>2840; 10695</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6537; 16700</t>
+          <t>3519; 11648</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1528; 10144</t>
+          <t>7852; 21729</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4000; 12599</t>
+          <t>2473; 9123</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3125; 10964</t>
+          <t>1290; 7411</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3869; 12193</t>
+          <t>6119; 16158</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8530; 22667</t>
+          <t>2069; 10139</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7589; 18908</t>
+          <t>6988; 17812</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5672; 15854</t>
+          <t>5295; 14549</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12012; 24727</t>
+          <t>12166; 24712</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11653; 29734</t>
+          <t>11966; 27916</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6228</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3089</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2994</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>4387</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2939</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2177</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>9770</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>6228</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>3089</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2994</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>14415</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2023; 8993</t>
+          <t>3119; 11158</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>731; 6355</t>
+          <t>985; 7340</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>715; 5852</t>
+          <t>1294; 7427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5607; 14168</t>
+          <t>2570; 10270</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3105; 11224</t>
+          <t>1551; 8788</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>731; 7540</t>
+          <t>688; 7040</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>976; 7534</t>
+          <t>716; 5850</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2800; 10720</t>
+          <t>6078; 14539</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6578; 16789</t>
+          <t>6515; 17114</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2397; 11161</t>
+          <t>2732; 10882</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2173; 10877</t>
+          <t>2176; 10308</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10342; 22647</t>
+          <t>9493; 20288</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4771</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5514</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4516</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2580</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7420</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2794</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4771</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5514</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6023</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6625</t>
+          <t>5933</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1651; 8705</t>
+          <t>1799; 10197</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6712</t>
+          <t>2236; 10508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4266; 12960</t>
+          <t>2808; 10995</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>626; 7745</t>
+          <t>673; 11564</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2179; 8963</t>
+          <t>1659; 9148</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2303; 10997</t>
+          <t>837; 6794</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2980; 10723</t>
+          <t>3747; 12750</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>908; 9686</t>
+          <t>514; 6587</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5385; 17227</t>
+          <t>5046; 16182</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4191; 14257</t>
+          <t>4014; 14952</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8436; 19815</t>
+          <t>8243; 19577</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2176; 13885</t>
+          <t>2317; 13275</t>
         </is>
       </c>
     </row>
@@ -2905,37 +2905,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1416</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2879</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4103</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2047</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>539</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>1190</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4140</t>
+          <t>0; 2892</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>659; 5063</t>
+          <t>1555; 8176</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>765; 6966</t>
+          <t>606; 5256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2753</t>
+          <t>0; 4098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2879</t>
+          <t>0; 4256</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1447; 7977</t>
+          <t>662; 5616</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>593; 5533</t>
+          <t>750; 6629</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 7336</t>
+          <t>0; 2676</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>690; 5037</t>
+          <t>695; 5012</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2968; 10670</t>
+          <t>3045; 12314</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2148; 9242</t>
+          <t>2088; 9417</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 8102</t>
+          <t>0; 3849</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2273</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6973</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2789</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1450</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>666</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1542</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2273</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>8355</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>698; 6370</t>
+          <t>0; 3826</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4907</t>
+          <t>721; 6078</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4402</t>
+          <t>0; 0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>388; 4543</t>
+          <t>3827; 13290</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3325</t>
+          <t>704; 6979</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>715; 5657</t>
+          <t>0; 5077</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 0</t>
+          <t>0; 3760</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4098; 14665</t>
+          <t>322; 4334</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1361; 7646</t>
+          <t>1348; 6977</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1406; 8195</t>
+          <t>1427; 8149</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 3664</t>
+          <t>0; 3079</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5274; 17295</t>
+          <t>4596; 14647</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>10167</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>14122</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>8438</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>18578</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3815</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>14212</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>10167</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>14122</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5762</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>34849</t>
+          <t>33861</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4809; 14006</t>
+          <t>6011; 15491</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>12477; 26022</t>
+          <t>9173; 21830</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1312; 7805</t>
+          <t>2582; 10996</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8932; 21018</t>
+          <t>13049; 27745</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6025; 16133</t>
+          <t>4431; 13922</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8648; 21256</t>
+          <t>12790; 25709</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2598; 10465</t>
+          <t>1304; 7362</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13520; 29896</t>
+          <t>9058; 21448</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12478; 25787</t>
+          <t>12573; 26533</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>24257; 43229</t>
+          <t>24127; 41955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5357; 15121</t>
+          <t>5551; 15754</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26128; 46161</t>
+          <t>24401; 43600</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>11694</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3930</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1563</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3949</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>13509</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>10387</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>3024</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>11694</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>9262</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>3930</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>5836</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1285; 7855</t>
+          <t>7073; 17017</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9088; 19808</t>
+          <t>5278; 14596</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6395; 15904</t>
+          <t>1323; 7865</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1219; 7722</t>
+          <t>300; 4423</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7050; 17123</t>
+          <t>1834; 8097</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4838; 14563</t>
+          <t>9047; 20260</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1377; 7981</t>
+          <t>6237; 16724</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>359; 5242</t>
+          <t>1817; 9480</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10510; 23153</t>
+          <t>10669; 22438</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16283; 30791</t>
+          <t>16160; 30547</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9850; 21153</t>
+          <t>9319; 21025</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2223; 9207</t>
+          <t>2845; 11379</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>54913</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>32961</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>48489</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>44723</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>37745</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>94550</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>24919; 42812</t>
+          <t>33274; 52542</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>39011; 60340</t>
+          <t>38616; 62296</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34721; 55716</t>
+          <t>28893; 48170</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29505; 50292</t>
+          <t>42903; 69325</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32699; 53374</t>
+          <t>24916; 42840</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38238; 61357</t>
+          <t>37802; 59783</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28628; 48785</t>
+          <t>34354; 55005</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>49117; 77960</t>
+          <t>30673; 51187</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>61541; 88920</t>
+          <t>61548; 88815</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>83051; 113810</t>
+          <t>84091; 114490</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67923; 96114</t>
+          <t>69808; 97438</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>86545; 123106</t>
+          <t>79571; 113243</t>
         </is>
       </c>
     </row>
